--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87b3b59ad8254f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcdf5fd61ae5245dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce842df698554d1c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfca040b80e944fb2"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcdf5fd61ae5245dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re74e9e57a107478c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfca040b80e944fb2"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6126c93729c4ded"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re74e9e57a107478c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2159bc2861b84c50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6126c93729c4ded"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1d33fa707bd4a7d"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2159bc2861b84c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re430e4d7dc514a4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1d33fa707bd4a7d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88397251afdc471f"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re430e4d7dc514a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R419bf6fcd5924a90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88397251afdc471f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R232fd639c7104f12"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R419bf6fcd5924a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R068c4709e16d4b08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R232fd639c7104f12"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a83ae4408104445"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R068c4709e16d4b08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd3a33fdcab94e92"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a83ae4408104445"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0eabf1e4936403a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd3a33fdcab94e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31dbf48166334d0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0eabf1e4936403a"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59a19214db944886"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31dbf48166334d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7fc90a29eea6452a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59a19214db944886"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c5f023f0bbd46a5"/>
 </x:worksheet>
 </file>